--- a/chapters/collection/store_observation.xlsx
+++ b/chapters/collection/store_observation.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>sensor</t>
+          <t>obs_A</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -577,7 +577,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>sensor</t>
+          <t>obs_B</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>obs_A</t>
+          <t>sensor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>obs_A</t>
+          <t>sensor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>sensor</t>
+          <t>obs_A</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>obs_A</t>
+          <t>sensor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -969,7 +969,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>sensor</t>
+          <t>obs_B</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>sensor</t>
+          <t>obs_A</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>obs_A</t>
+          <t>sensor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1588,7 +1588,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Notes for the analyst</t>
+          <t>Notes for the analyst (a realistic teaching dataset written for the book)</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Time-sampling: you cannot watch 24/7 — the slots you choose are a sample over time.</t>
+          <t>Time-sampling: you cannot watch 24/7, so the slots you choose are a sample over time.</t>
         </is>
       </c>
     </row>
